--- a/product_upload/packages/20/file.xlsx
+++ b/product_upload/packages/20/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>FUCIDIN 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-2772C9FF868A</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>FORTICEF 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-B8AFF8E42883</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1204,6 +1219,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>FORMIT 850 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-F560EFD1FB54</t>
         </is>
       </c>
@@ -1227,7 +1247,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>FOLIC ACID</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-0AD553EB8F37</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1584,6 +1609,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>FOLIC ACID</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-222A22D0549D</t>
         </is>
       </c>
@@ -1607,7 +1637,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1770,6 +1800,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>FML 0.1% ophthalmic suspension</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-E7EE03B87D2C</t>
         </is>
       </c>
@@ -1793,7 +1828,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1966,6 +2001,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>FORTZAAR 100/25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-AD96A1B33543</t>
         </is>
       </c>
@@ -1989,7 +2029,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2156,6 +2196,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>FOSAMAX ONCE WEEKLY 70MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-2910BA1EDDBD</t>
         </is>
       </c>
@@ -2179,7 +2224,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2346,6 +2391,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>FUCICORT 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B493496EA2A8</t>
         </is>
       </c>
@@ -2369,7 +2419,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2528,6 +2578,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FROBEN TAB 50MG</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-8280B2B0A67D</t>
         </is>
       </c>
@@ -2551,7 +2606,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2714,6 +2769,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>FROBEN TAB 50MG</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-05EBBF2C1D7A</t>
         </is>
       </c>
@@ -2737,7 +2797,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2900,6 +2960,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>FROBEN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-1C71B89675AC</t>
         </is>
       </c>
@@ -2923,7 +2988,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3078,6 +3143,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FROBEN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-D054CCD951C6</t>
         </is>
       </c>
@@ -3101,7 +3171,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3272,6 +3342,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>FUCIDIN 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-F2CE137D5B0F</t>
         </is>
       </c>
@@ -3295,7 +3370,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3462,6 +3537,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>FOSTIMON HP 75 IU VIAL (IM) USE</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-F271AEB0C61F</t>
         </is>
       </c>
@@ -3485,7 +3565,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3656,6 +3736,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>FOSTIMON HP 150 IU VIAL IM(WOMEN URIN)</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-190D5C017B87</t>
         </is>
       </c>
@@ -3679,7 +3764,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3850,6 +3935,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>FOSTER PRESSURISED SOLUTION FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-B04FC3340D10</t>
         </is>
       </c>
@@ -3873,7 +3963,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4048,6 +4138,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>GLOCLAV 625MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-217B7F336064</t>
         </is>
       </c>
@@ -4071,7 +4166,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4248,6 +4343,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>GANFORT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-83D16419B975</t>
         </is>
       </c>
@@ -4271,7 +4371,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4442,6 +4542,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>GLIDE 3MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-AB5F3F8066A3</t>
         </is>
       </c>
@@ -4465,7 +4570,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4620,6 +4725,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>GLIDE 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-0112DF75CFC7</t>
         </is>
       </c>
@@ -4643,7 +4753,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>GLIDE 1MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-0147D3D90BFE</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4992,6 +5107,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>GLIBIL-5 TABS</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-92046A7B6234</t>
         </is>
       </c>
@@ -5015,7 +5135,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5170,6 +5290,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>GLAZE 80MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-83A69FD53940</t>
         </is>
       </c>
@@ -5193,7 +5318,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5356,6 +5481,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>GLAZE 80MG TAB</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-9238B024F557</t>
         </is>
       </c>
@@ -5379,7 +5509,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5546,6 +5676,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>GLADOS 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-97B1E7A8246B</t>
         </is>
       </c>
@@ -5569,7 +5704,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5732,6 +5867,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>GLADOS 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-42D3FD879E85</t>
         </is>
       </c>
@@ -5755,7 +5895,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5926,6 +6066,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>GLACERA 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-457722310E98</t>
         </is>
       </c>
@@ -5949,7 +6094,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6116,6 +6261,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>GLACERA 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-00776A2F0AF5</t>
         </is>
       </c>
@@ -6139,7 +6289,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6298,6 +6448,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>GINSANA TONIC 140MG-15ML</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-E56C45096B48</t>
         </is>
       </c>
@@ -6321,7 +6476,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6484,6 +6639,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>GLIDE 4MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-9036ECDDAD6E</t>
         </is>
       </c>
@@ -6507,7 +6667,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6678,6 +6838,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>GLIM 1MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-05DA8E981699</t>
         </is>
       </c>
@@ -6701,7 +6866,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6872,6 +7037,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>GLIM 2MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-6829B2651857</t>
         </is>
       </c>
@@ -6895,7 +7065,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7062,6 +7232,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>GLIM 3MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-CDAD4B2695A6</t>
         </is>
       </c>
@@ -7085,7 +7260,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7260,6 +7435,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>GLOCLAV 1GM FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-567561A013B2</t>
         </is>
       </c>
@@ -7283,7 +7463,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7446,6 +7626,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>GLITRA 4MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-F9D4EA837A3D</t>
         </is>
       </c>
@@ -7469,7 +7654,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7636,6 +7821,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>GLITRA 3MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-DD851E9757BA</t>
         </is>
       </c>
@@ -7659,7 +7849,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7830,6 +8020,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>GLITRA 2MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-125F76FECD84</t>
         </is>
       </c>
@@ -7853,7 +8048,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8024,6 +8219,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>GLITRA 1MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-F216F8EB26B2</t>
         </is>
       </c>
@@ -8047,7 +8247,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8206,6 +8406,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>GINSANA 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-7F9FEF58B573</t>
         </is>
       </c>
@@ -8229,7 +8434,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8406,6 +8611,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>GLIPTEN 100MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-7C64D6DE136C</t>
         </is>
       </c>
@@ -8429,7 +8639,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8586,6 +8796,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t xml:space="preserve">GLIPTAMET </t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-AAB3095D1EB9</t>
         </is>
       </c>
@@ -8609,7 +8824,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8772,6 +8987,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>GLIPOM 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-7E589B7A5C18</t>
         </is>
       </c>
@@ -8795,7 +9015,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8962,6 +9182,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>GLIM 6MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-42710D73518E</t>
         </is>
       </c>
@@ -8985,7 +9210,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9156,6 +9381,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>GLIM 4MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-05F7AE361E81</t>
         </is>
       </c>
@@ -9179,7 +9409,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9344,6 +9574,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>GLIPTAMET</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-AF7FBF24791E</t>
         </is>
       </c>
@@ -9367,7 +9602,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9538,6 +9773,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>GILENYA 0.5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-87E361C47427</t>
         </is>
       </c>
@@ -9561,7 +9801,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9728,6 +9968,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>GENURIN FORT 200 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-DC3AD275685B</t>
         </is>
       </c>
@@ -9751,7 +9996,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9926,6 +10171,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>GAVISCON DOUBLE ACTION CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-AB2B2DCFE93F</t>
         </is>
       </c>
@@ -9949,7 +10199,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10112,6 +10362,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>GAVISCON COOL CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-7DF9A984D7EB</t>
         </is>
       </c>
@@ -10135,7 +10390,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10302,6 +10557,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>GAVISCON ADVANCE PEPPERMINT FLAVOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-FACA2FDBE9EB</t>
         </is>
       </c>
@@ -10325,7 +10585,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10492,6 +10752,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>GASTROZOLE</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-7F731F53872F</t>
         </is>
       </c>
@@ -10515,7 +10780,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10682,6 +10947,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>GASTROFAIT TAB 500MG</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-9032F699D88D</t>
         </is>
       </c>
@@ -10705,7 +10975,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10868,6 +11138,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-74C26F41545C</t>
         </is>
       </c>
@@ -10891,7 +11166,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11058,6 +11333,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-5F5823135FB4</t>
         </is>
       </c>
@@ -11081,7 +11361,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11248,6 +11528,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-898A9ECA691C</t>
         </is>
       </c>
@@ -11271,7 +11556,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11438,6 +11723,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-3F0473884917</t>
         </is>
       </c>
@@ -11461,7 +11751,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11624,6 +11914,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>GAPENTIN</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-E82520BDF492</t>
         </is>
       </c>
@@ -11647,7 +11942,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11810,6 +12105,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>GAPENTIN</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-6E09EB2593A2</t>
         </is>
       </c>
@@ -11833,7 +12133,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12000,6 +12300,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>GAVISCON DOUBLE ACTION CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-924F0A96A13A</t>
         </is>
       </c>
@@ -12023,7 +12328,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12190,6 +12495,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>GAVISCON DOUBLE ACTION ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-79A3D2A89B9A</t>
         </is>
       </c>
@@ -12213,7 +12523,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12380,6 +12690,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>GAVISCON EXTRA STRENGTH PEPPER.CHEW. TAB</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-A98D1844464F</t>
         </is>
       </c>
@@ -12403,7 +12718,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12574,6 +12889,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>GAVISCON ORIGINAL ANISEED ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-C4E872CB7AC4</t>
         </is>
       </c>
@@ -12597,7 +12917,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12756,6 +13076,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>GENURIN 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-E7459EC73A18</t>
         </is>
       </c>
@@ -12779,7 +13104,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12950,6 +13275,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>GENTACIN</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-8A1812D1A213</t>
         </is>
       </c>
@@ -12973,7 +13303,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13140,6 +13470,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>GENTACIN</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-81B7677F63E5</t>
         </is>
       </c>
@@ -13163,7 +13498,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13326,6 +13661,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>GENPRID</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-8A7D642BA622</t>
         </is>
       </c>
@@ -13349,7 +13689,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13516,6 +13856,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>GENPRID</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-6D230A0ADB35</t>
         </is>
       </c>
@@ -13539,7 +13884,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13698,6 +14043,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>GIAD 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-DF2A41304A05</t>
         </is>
       </c>
@@ -13721,7 +14071,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13888,6 +14238,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>GAVISCON PEPPERMINT LIQUID</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-F5B4DC0D71D9</t>
         </is>
       </c>
@@ -13911,7 +14266,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14074,6 +14429,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>GAVISCON PEPPERMINT CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-AE586CDAA8AB</t>
         </is>
       </c>
@@ -14097,7 +14457,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14266,6 +14626,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ISOPTIN S.R 240MG F.COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-195F2C6C3569</t>
         </is>
       </c>
@@ -14289,7 +14654,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14456,6 +14821,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ISOPTIN RETARD TAB 120MG</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-4ED36DF3D256</t>
         </is>
       </c>
@@ -14479,7 +14849,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14642,6 +15012,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>ISOCAINE 3 % CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-BA97F265553B</t>
         </is>
       </c>
@@ -14665,7 +15040,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14836,6 +15211,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ISOBIDE</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-AB8ED2993BA8</t>
         </is>
       </c>
@@ -14859,7 +15239,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15030,6 +15410,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>ISOBIDE</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-BAF1FF1DC45B</t>
         </is>
       </c>
@@ -15053,7 +15438,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15220,6 +15605,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>IROKID 50MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-0E5A8A6D3AE2</t>
         </is>
       </c>
@@ -15243,7 +15633,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15418,6 +15808,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>I-PROFEN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-AAA72A68FF80</t>
         </is>
       </c>
@@ -15441,7 +15836,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15608,6 +16003,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>IPRAMAX 25 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-003F989D427C</t>
         </is>
       </c>
@@ -15631,7 +16031,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15794,6 +16194,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>IPRAMAX 100 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-1AE7FA3BCDC8</t>
         </is>
       </c>
@@ -15817,7 +16222,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15990,6 +16395,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ISOPTIN TABLETS 40 MG.</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-AD51D6ABE642</t>
         </is>
       </c>
@@ -16013,7 +16423,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16182,6 +16592,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ISOPTIN TABLETS 80 MG.</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-FB3CC495A121</t>
         </is>
       </c>
@@ -16205,7 +16620,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16364,6 +16779,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ISOTRIRAUPINE S.P.TAB</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-91942C0F5C5D</t>
         </is>
       </c>
@@ -16387,7 +16807,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16550,6 +16970,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>JOINTACE COLLAGEN TABLET</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-2C68D1A349DB</t>
         </is>
       </c>
@@ -16573,7 +16998,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16744,6 +17169,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>JOINT CARE MAX CAPSULES AND TABLETS</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-BD7060C39770</t>
         </is>
       </c>
@@ -16767,7 +17197,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16926,6 +17356,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>JOFLAM 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-FFDDC727EE2E</t>
         </is>
       </c>
@@ -16949,7 +17384,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17120,6 +17555,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>JEDCORENE EFFERVESCENT GRANULES</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-369A703DE8AA</t>
         </is>
       </c>
@@ -17143,7 +17583,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17310,6 +17750,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>JEDCOMAG EFFERVESCENT GRANULES5GM SACHET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-D3CCC59791CA</t>
         </is>
       </c>
@@ -17333,7 +17778,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17496,6 +17941,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>JEDCOFLACIN 200MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-DD772D9E3CC2</t>
         </is>
       </c>
@@ -17519,7 +17969,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17682,6 +18132,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>JEDCO CAL - C EFFERVESCENT GRANULES</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-212AAD215BA2</t>
         </is>
       </c>
@@ -17705,7 +18160,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17868,6 +18323,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>JAZOFEN 200 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-05BB051EE965</t>
         </is>
       </c>
@@ -17891,7 +18351,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18058,6 +18518,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>IVARIN 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-5A87E8188BB0</t>
         </is>
       </c>
@@ -18081,7 +18546,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18248,6 +18713,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>IVARIN 40MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-2F55A6790EF8</t>
         </is>
       </c>
@@ -18271,7 +18741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18442,6 +18912,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>IVARIN 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-A6F39CAA15BD</t>
         </is>
       </c>
@@ -18465,7 +18940,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18636,6 +19111,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>IVARIN 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-FD301CBFE39A</t>
         </is>
       </c>
@@ -18659,7 +19139,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18826,6 +19306,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>ITRAZOL 100 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-465574CFFE70</t>
         </is>
       </c>
@@ -18849,7 +19334,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19016,6 +19501,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>ITRAZOL 100 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-2BF22F3F3C34</t>
         </is>
       </c>
@@ -19039,7 +19529,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19210,6 +19700,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>JAZOFEN 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-2FC08F5B7F06</t>
         </is>
       </c>
@@ -19233,7 +19728,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19396,6 +19891,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>JOINTACE COLLAGEN TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-F7F59CD9F77C</t>
         </is>
       </c>
@@ -19419,7 +19919,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19585,6 +20085,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>INSULATARD PENFILL</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-6D6783882703</t>
         </is>
@@ -19601,7 +20106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19647,100 +20152,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19772,7 +20282,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19787,92 +20297,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-42870</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>51.05</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>120</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19904,7 +20419,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19919,92 +20434,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-98959</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>428.88</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>121</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20036,7 +20556,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20051,92 +20571,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-53231</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>356.54</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>122</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20168,7 +20693,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20183,92 +20708,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-27711</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>115.18</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>123</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20300,7 +20830,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20315,92 +20845,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-27991</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>237.96</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>124</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20432,7 +20967,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20447,92 +20982,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-99072</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>378.91</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>125</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20564,7 +21104,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20579,92 +21119,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-26418</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>126</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20696,7 +21241,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20711,92 +21256,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-20205</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>256.78</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>127</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20828,7 +21378,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20843,92 +21393,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-71103</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>139.69</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>128</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20960,7 +21515,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20975,92 +21530,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-41682</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>224.69</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>129</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21092,7 +21652,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21107,92 +21667,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-39339</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>237.32</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>130</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21209,7 +21774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21315,6 +21880,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21350,7 +21925,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21415,6 +21990,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-C42C8F905F73</t>
         </is>
@@ -21451,7 +22036,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21516,6 +22101,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-D51BC134343F</t>
         </is>
@@ -21552,7 +22147,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21617,6 +22212,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-C5B7841D1D2E</t>
         </is>
@@ -21653,7 +22258,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21718,6 +22323,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-E595790870B9</t>
         </is>
@@ -21754,7 +22369,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21819,6 +22434,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-1AFA2C79E4E8</t>
         </is>
@@ -21855,7 +22480,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21920,6 +22545,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-665D180B6B0E</t>
         </is>
@@ -21956,7 +22591,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22021,6 +22656,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-91F930EB2007</t>
         </is>
@@ -22057,7 +22702,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22122,6 +22767,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A3114100D4C5</t>
         </is>
@@ -22158,7 +22813,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22223,6 +22878,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-F382AE96BE81</t>
         </is>
@@ -22259,7 +22924,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22324,6 +22989,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-951CAFAFFCC3</t>
         </is>
@@ -22360,7 +23035,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22425,6 +23100,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-5F732384D810</t>
         </is>
@@ -22461,7 +23146,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22526,6 +23211,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-05C9255F386E</t>
         </is>
@@ -22562,7 +23257,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22627,6 +23322,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-6FA2C2C7C1E1</t>
         </is>
@@ -22663,7 +23368,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22728,6 +23433,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-30255D3CD533</t>
         </is>
@@ -22764,7 +23479,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22829,6 +23544,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-5963A773C60E</t>
         </is>
@@ -22865,7 +23590,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22930,6 +23655,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-FC1B478CFAE2</t>
         </is>
@@ -22966,7 +23701,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23031,6 +23766,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-5E0D59B3CF90</t>
         </is>
@@ -23067,7 +23812,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23132,6 +23877,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-59AB058EC67B</t>
         </is>
@@ -23168,7 +23923,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23233,6 +23988,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-7A0D5D4A5C1F</t>
         </is>
@@ -23269,7 +24034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23334,6 +24099,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-40223F926B2E</t>
         </is>

--- a/product_upload/packages/20/file.xlsx
+++ b/product_upload/packages/20/file.xlsx
@@ -877,8 +877,16 @@
           <t>4740648555-174-416558721771</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FORTICEF 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FORTICEF 500MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1064,8 +1072,16 @@
           <t>1332428409-097-132298109604</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FORMIT 850 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FORMIT 850 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1645,8 +1661,16 @@
           <t>1941660846-415-602341595036</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FML 0.1% ophthalmic suspension</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FML 0.1% ophthalmic suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2427,8 +2451,16 @@
           <t>4407596636-681-633672733710</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FROBEN TAB 50MG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FROBEN TAB 50MG detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2614,8 +2646,16 @@
           <t>5923009661-966-772603628430</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FROBEN TAB 50MG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FROBEN TAB 50MG detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2805,8 +2845,16 @@
           <t>1163615287-722-966106120442</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FROBEN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FROBEN TAB 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2996,8 +3044,16 @@
           <t>6754515975-431-458416873242</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FROBEN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FROBEN TAB 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -4578,8 +4634,16 @@
           <t>4064465824-238-321959610000</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIDE 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>GLIDE 2MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4761,8 +4825,16 @@
           <t>8383498342-545-045375906480</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIDE 1MG TABLET</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>GLIDE 1MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5143,8 +5215,16 @@
           <t>1838919709-487-308357534207</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLAZE 80MG TAB</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>GLAZE 80MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5326,8 +5406,16 @@
           <t>1236003145-649-619294680221</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLAZE 80MG TAB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>GLAZE 80MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -6297,8 +6385,16 @@
           <t>7784679164-939-799045962356</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GINSANA TONIC 140MG-15ML</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>GINSANA TONIC 140MG-15ML detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6484,8 +6580,16 @@
           <t>7733419264-270-347764771711</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIDE 4MG TABLET</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>GLIDE 4MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -8255,8 +8359,16 @@
           <t>6775886250-275-491241981352</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GINSANA 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>GINSANA 100MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8647,8 +8759,16 @@
           <t>3060097943-523-054241733693</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIPTAMET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>GLIPTAMET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -8832,8 +8952,16 @@
           <t>0308755773-842-280293824278</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIPOM 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>GLIPOM 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9417,8 +9545,16 @@
           <t>4352647602-435-417228752619</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLIPTAMET</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>GLIPTAMET detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -10207,8 +10343,16 @@
           <t>9556146446-923-966565228950</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVISCON COOL CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>GAVISCON COOL CHEWABLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -12141,8 +12285,16 @@
           <t>8743287368-991-532772667073</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVISCON DOUBLE ACTION CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>GAVISCON DOUBLE ACTION CHEWABLE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12925,8 +13077,16 @@
           <t>1031484104-956-168933324298</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GENURIN 100MG TAB</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>GENURIN 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13892,8 +14052,16 @@
           <t>6673585911-791-488027484373</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GIAD 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>GIAD 50 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14662,8 +14830,16 @@
           <t>7596332782-062-023114838021</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISOPTIN RETARD TAB 120MG</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ISOPTIN RETARD TAB 120MG detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14857,8 +15033,16 @@
           <t>5943603242-353-974122073462</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISOCAINE 3 % CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ISOCAINE 3 % CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15446,8 +15630,16 @@
           <t>9534224852-489-199020094296</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IROKID 50MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>IROKID 50MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -16628,8 +16820,16 @@
           <t>3000661485-716-118321714291</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISOTRIRAUPINE S.P.TAB</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ISOTRIRAUPINE S.P.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16815,8 +17015,16 @@
           <t>1362619481-036-437667144310</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JOINTACE COLLAGEN TABLET</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>JOINTACE COLLAGEN TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17205,8 +17413,16 @@
           <t>5934009544-310-398954025130</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JOFLAM 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>JOFLAM 50MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17786,8 +18002,16 @@
           <t>6754874802-833-564721295190</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JEDCOFLACIN 200MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>JEDCOFLACIN 200MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17977,8 +18201,16 @@
           <t>6343613313-393-775804825339</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JEDCO CAL - C EFFERVESCENT GRANULES</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>JEDCO CAL - C EFFERVESCENT GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18168,8 +18400,16 @@
           <t>2282353743-069-010853803831</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JAZOFEN 200 MG TAB</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>JAZOFEN 200 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -19927,8 +20167,16 @@
           <t>4908068728-249-938026890282</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INSULATARD PENFILL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>INSULATARD PENFILL detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/20/file.xlsx
+++ b/product_upload/packages/20/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22022,7 +22022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22103,40 +22103,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22216,38 +22221,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>486.79</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-C42C8F905F73</t>
         </is>
@@ -22327,38 +22337,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>413.97</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-D51BC134343F</t>
         </is>
@@ -22438,38 +22453,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>472.43</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-C5B7841D1D2E</t>
         </is>
@@ -22549,38 +22569,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>190.23</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-E595790870B9</t>
         </is>
@@ -22660,38 +22685,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>343.93</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-1AFA2C79E4E8</t>
         </is>
@@ -22771,38 +22801,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>331.86</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-665D180B6B0E</t>
         </is>
@@ -22882,38 +22917,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>335.4</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-91F930EB2007</t>
         </is>
@@ -22993,38 +23033,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>241.16</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A3114100D4C5</t>
         </is>
@@ -23104,38 +23149,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>48.33</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-F382AE96BE81</t>
         </is>
@@ -23215,38 +23265,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>91.95999999999999</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-951CAFAFFCC3</t>
         </is>
@@ -23326,38 +23381,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>348.33</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-5F732384D810</t>
         </is>
@@ -23437,38 +23497,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>49.42</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-05C9255F386E</t>
         </is>
@@ -23548,38 +23613,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>320.65</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-6FA2C2C7C1E1</t>
         </is>
@@ -23659,38 +23729,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-30255D3CD533</t>
         </is>
@@ -23770,38 +23845,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>444.87</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-5963A773C60E</t>
         </is>
@@ -23881,38 +23961,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>46.84</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-FC1B478CFAE2</t>
         </is>
@@ -23992,38 +24077,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>294.63</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-5E0D59B3CF90</t>
         </is>
@@ -24103,38 +24193,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>75.5</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-59AB058EC67B</t>
         </is>
@@ -24214,38 +24309,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>138.57</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-7A0D5D4A5C1F</t>
         </is>
@@ -24325,38 +24425,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>460.05</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-40223F926B2E</t>
         </is>
